--- a/data/trans_camb/IP1016-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1016-Estudios-trans_camb.xlsx
@@ -787,7 +787,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,83</t>
+          <t>0,0; 0,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -802,17 +802,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,96</t>
+          <t>0,0; 0,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,41</t>
+          <t>0,0; 0,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,46</t>
+          <t>0,0; 0,45</t>
         </is>
       </c>
     </row>
@@ -1114,17 +1114,17 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,46</t>
+          <t>0,0; 0,57</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,25</t>
+          <t>0,0; 0,23</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,27</t>
+          <t>0,0; 0,3</t>
         </is>
       </c>
     </row>
